--- a/data/raw/inventory/Week 33/Tonor/Vendor SOH (SP-API).xlsx
+++ b/data/raw/inventory/Week 33/Tonor/Vendor SOH (SP-API).xlsx
@@ -67,325 +67,325 @@
     <t>SnapshotDate</t>
   </si>
   <si>
+    <t>FBK77102</t>
+  </si>
+  <si>
     <t>FBA77106</t>
   </si>
   <si>
+    <t>FBA79574</t>
+  </si>
+  <si>
+    <t>FBA79113</t>
+  </si>
+  <si>
+    <t>FBA79114</t>
+  </si>
+  <si>
+    <t>FBA77103</t>
+  </si>
+  <si>
+    <t>FBA79115</t>
+  </si>
+  <si>
+    <t>FBA77110</t>
+  </si>
+  <si>
+    <t>FBA79576</t>
+  </si>
+  <si>
+    <t>FBA79116</t>
+  </si>
+  <si>
+    <t>FBA77111</t>
+  </si>
+  <si>
+    <t>FBA77105</t>
+  </si>
+  <si>
     <t>FBA79577</t>
   </si>
   <si>
+    <t>FBA79582</t>
+  </si>
+  <si>
+    <t>FBA79575</t>
+  </si>
+  <si>
+    <t>FBA77104</t>
+  </si>
+  <si>
+    <t>FBA77115</t>
+  </si>
+  <si>
     <t>FBA79578</t>
   </si>
   <si>
     <t>FBA77113</t>
   </si>
   <si>
-    <t>FBA79574</t>
-  </si>
-  <si>
-    <t>FBA79116</t>
-  </si>
-  <si>
-    <t>FBA77103</t>
+    <t>FBA79111</t>
   </si>
   <si>
     <t>FBA79579</t>
   </si>
   <si>
-    <t>FBA77105</t>
-  </si>
-  <si>
-    <t>FBA79582</t>
-  </si>
-  <si>
     <t>FBA77117</t>
   </si>
   <si>
-    <t>FBA79111</t>
-  </si>
-  <si>
     <t>FBA77101</t>
   </si>
   <si>
     <t>FBA77116</t>
   </si>
   <si>
-    <t>FBA79113</t>
+    <t>FBA79585</t>
+  </si>
+  <si>
+    <t>FBA79696</t>
   </si>
   <si>
     <t>FBA79697</t>
   </si>
   <si>
-    <t>FBA77111</t>
-  </si>
-  <si>
-    <t>FBA79115</t>
-  </si>
-  <si>
-    <t>FBA79114</t>
-  </si>
-  <si>
-    <t>FBA77115</t>
-  </si>
-  <si>
-    <t>FBA79576</t>
-  </si>
-  <si>
-    <t>FBK77102</t>
-  </si>
-  <si>
-    <t>FBA79575</t>
-  </si>
-  <si>
-    <t>FBA77110</t>
-  </si>
-  <si>
-    <t>FBA77104</t>
-  </si>
-  <si>
     <t>FBA77114</t>
   </si>
   <si>
-    <t>FBA79696</t>
-  </si>
-  <si>
-    <t>FBA79585</t>
+    <t>B07GVGMW59</t>
   </si>
   <si>
     <t>B082W4B7SX</t>
   </si>
   <si>
+    <t>B0B4WTHLX5</t>
+  </si>
+  <si>
+    <t>B0BTCXQQ6M</t>
+  </si>
+  <si>
+    <t>B0CCV74CL7</t>
+  </si>
+  <si>
+    <t>B09Z5Q194D</t>
+  </si>
+  <si>
+    <t>B0C8JDHLX9</t>
+  </si>
+  <si>
+    <t>B08NDB5NWP</t>
+  </si>
+  <si>
+    <t>B0BRCR2QQ7</t>
+  </si>
+  <si>
+    <t>B0BYHHSLPC</t>
+  </si>
+  <si>
+    <t>B08CVP2HXP</t>
+  </si>
+  <si>
+    <t>B089FVQD3Z</t>
+  </si>
+  <si>
     <t>B0CSCT63BL</t>
   </si>
   <si>
+    <t>B0CCVBQRFX</t>
+  </si>
+  <si>
+    <t>B0BG8CJXHH</t>
+  </si>
+  <si>
+    <t>B089SJGQBH</t>
+  </si>
+  <si>
+    <t>B08V1JS3NY</t>
+  </si>
+  <si>
     <t>B0CFKZ72N7</t>
   </si>
   <si>
     <t>B01ISNU3X4</t>
   </si>
   <si>
-    <t>B0B4WTHLX5</t>
-  </si>
-  <si>
-    <t>B0BYHHSLPC</t>
-  </si>
-  <si>
-    <t>B09Z5Q194D</t>
+    <t>B0BRKFP94K</t>
   </si>
   <si>
     <t>B0CQX4GVSB</t>
   </si>
   <si>
-    <t>B089FVQD3Z</t>
-  </si>
-  <si>
-    <t>B0CCVBQRFX</t>
-  </si>
-  <si>
     <t>B078WNW4YW</t>
   </si>
   <si>
-    <t>B0BRKFP94K</t>
-  </si>
-  <si>
     <t>B07WLWN2ZT</t>
   </si>
   <si>
     <t>B0BBL47VR5</t>
   </si>
   <si>
-    <t>B0BTCXQQ6M</t>
+    <t>B0CFKHCQ8W</t>
+  </si>
+  <si>
+    <t>B0CQX3VB1R</t>
   </si>
   <si>
     <t>B0CQX4K9P5</t>
   </si>
   <si>
-    <t>B08CVP2HXP</t>
-  </si>
-  <si>
-    <t>B0C8JDHLX9</t>
-  </si>
-  <si>
-    <t>B0CCV74CL7</t>
-  </si>
-  <si>
-    <t>B08V1JS3NY</t>
-  </si>
-  <si>
-    <t>B0BRCR2QQ7</t>
-  </si>
-  <si>
-    <t>B07GVGMW59</t>
-  </si>
-  <si>
-    <t>B0BG8CJXHH</t>
-  </si>
-  <si>
-    <t>B08NDB5NWP</t>
-  </si>
-  <si>
-    <t>B089SJGQBH</t>
-  </si>
-  <si>
     <t>B07TSN2H9D</t>
   </si>
   <si>
-    <t>B0CQX3VB1R</t>
-  </si>
-  <si>
-    <t>B0CFKHCQ8W</t>
-  </si>
-  <si>
     <t>Tonor</t>
   </si>
   <si>
+    <t>G11</t>
+  </si>
+  <si>
     <t>T20</t>
   </si>
   <si>
+    <t>TC30S</t>
+  </si>
+  <si>
+    <t>TC310</t>
+  </si>
+  <si>
+    <t>TC310+</t>
+  </si>
+  <si>
+    <t>ORCA001</t>
+  </si>
+  <si>
+    <t>T10</t>
+  </si>
+  <si>
+    <t>TM20</t>
+  </si>
+  <si>
+    <t>TC30S+</t>
+  </si>
+  <si>
+    <t>TC-777 PRO</t>
+  </si>
+  <si>
+    <t>TC30</t>
+  </si>
+  <si>
+    <t>T30</t>
+  </si>
+  <si>
     <t>TM310</t>
   </si>
   <si>
+    <t>TD510+</t>
+  </si>
+  <si>
+    <t>TC30+</t>
+  </si>
+  <si>
+    <t>TC20</t>
+  </si>
+  <si>
+    <t>TC40</t>
+  </si>
+  <si>
     <t>D5</t>
   </si>
   <si>
     <t>K1</t>
   </si>
   <si>
-    <t>TC30S</t>
-  </si>
-  <si>
-    <t>TC-777 PRO</t>
-  </si>
-  <si>
-    <t>ORCA001</t>
+    <t>TD510</t>
   </si>
   <si>
     <t>D2</t>
   </si>
   <si>
-    <t>T30</t>
-  </si>
-  <si>
-    <t>TD510+</t>
-  </si>
-  <si>
     <t>S20</t>
   </si>
   <si>
-    <t>TD510</t>
-  </si>
-  <si>
     <t>TC-777</t>
   </si>
   <si>
     <t>TC40S</t>
   </si>
   <si>
-    <t>TC310</t>
+    <t>T20LP</t>
+  </si>
+  <si>
+    <t>TD310+</t>
   </si>
   <si>
     <t>TD310</t>
   </si>
   <si>
-    <t>TC30</t>
-  </si>
-  <si>
-    <t>T10</t>
-  </si>
-  <si>
-    <t>TC310+</t>
-  </si>
-  <si>
-    <t>TC40</t>
-  </si>
-  <si>
-    <t>TC30S+</t>
-  </si>
-  <si>
-    <t>G11</t>
-  </si>
-  <si>
-    <t>TC30+</t>
-  </si>
-  <si>
-    <t>TM20</t>
-  </si>
-  <si>
-    <t>TC20</t>
-  </si>
-  <si>
     <t>TC-2030</t>
   </si>
   <si>
-    <t>TD310+</t>
-  </si>
-  <si>
-    <t>T20LP</t>
+    <t>Conference Microphone</t>
   </si>
   <si>
     <t>Accessories</t>
   </si>
   <si>
-    <t>Conference Microphone</t>
+    <t>Condenser Microphone</t>
   </si>
   <si>
     <t>Dynamic Microphone</t>
   </si>
   <si>
-    <t>Condenser Microphone</t>
+    <t>Wired</t>
   </si>
   <si>
     <t>Boom Arm Kit</t>
   </si>
   <si>
-    <t>Wired</t>
+    <t>Tripod+RGB</t>
+  </si>
+  <si>
+    <t>Tripod - RGB</t>
+  </si>
+  <si>
+    <t>Boom Arm Kit - USB - RGB</t>
+  </si>
+  <si>
+    <t>Stand</t>
+  </si>
+  <si>
+    <t>Boom Arm Kit + RGB</t>
+  </si>
+  <si>
+    <t>Tripod</t>
+  </si>
+  <si>
+    <t>Hand held Mic + Boom Arm</t>
+  </si>
+  <si>
+    <t>Boom Arm Kit - XLR</t>
+  </si>
+  <si>
+    <t>Boom Arm Kit - USB</t>
   </si>
   <si>
     <t>Hand held Mic</t>
   </si>
   <si>
-    <t>Tripod+RGB</t>
-  </si>
-  <si>
-    <t>Tripod - RGB</t>
-  </si>
-  <si>
-    <t>Stand</t>
-  </si>
-  <si>
-    <t>Hand held Mic + Boom Arm</t>
+    <t>USB/XLR Mic</t>
   </si>
   <si>
     <t>Microphone Isolation Shield</t>
   </si>
   <si>
-    <t>USB/XLR Mic</t>
-  </si>
-  <si>
-    <t>Tripod</t>
-  </si>
-  <si>
-    <t>Boom Arm Kit - USB - RGB</t>
+    <t>Low Profile Boom Arm</t>
   </si>
   <si>
     <t>Hand held Mic + Stand</t>
   </si>
   <si>
-    <t>Boom Arm Kit - USB</t>
-  </si>
-  <si>
-    <t>Boom Arm Kit + RGB</t>
-  </si>
-  <si>
-    <t>Boom Arm Kit - XLR</t>
-  </si>
-  <si>
-    <t>Low Profile Boom Arm</t>
-  </si>
-  <si>
     <t>1p</t>
   </si>
   <si>
-    <t>2026-08-14</t>
+    <t>2026-08-15</t>
   </si>
 </sst>
 </file>
@@ -819,10 +819,10 @@
         <v>106</v>
       </c>
       <c r="H2">
-        <v>1164</v>
+        <v>1108</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J2" t="s">
         <v>122</v>
@@ -831,13 +831,16 @@
         <v>33</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N2">
         <v>0</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="P2">
+        <v>56577.57</v>
       </c>
       <c r="Q2" t="s">
         <v>123</v>
@@ -863,10 +866,10 @@
         <v>107</v>
       </c>
       <c r="H3">
-        <v>965</v>
+        <v>1164</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="s">
         <v>122</v>
@@ -875,16 +878,13 @@
         <v>33</v>
       </c>
       <c r="M3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3">
         <v>0</v>
-      </c>
-      <c r="P3">
-        <v>2333.97</v>
       </c>
       <c r="Q3" t="s">
         <v>123</v>
@@ -910,7 +910,7 @@
         <v>108</v>
       </c>
       <c r="H4">
-        <v>1688</v>
+        <v>1448</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -922,7 +922,7 @@
         <v>33</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N4">
         <v>0</v>
@@ -951,13 +951,13 @@
         <v>104</v>
       </c>
       <c r="F5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H5">
-        <v>848</v>
+        <v>1206</v>
       </c>
       <c r="I5">
-        <v>102</v>
+        <v>3</v>
       </c>
       <c r="J5" t="s">
         <v>122</v>
@@ -966,16 +966,16 @@
         <v>33</v>
       </c>
       <c r="M5">
-        <v>99</v>
+        <v>2</v>
       </c>
       <c r="N5">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="O5">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="P5">
-        <v>132959.66</v>
+        <v>5253.47</v>
       </c>
       <c r="Q5" t="s">
         <v>123</v>
@@ -995,16 +995,16 @@
         <v>78</v>
       </c>
       <c r="E6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H6">
-        <v>1448</v>
+        <v>1689</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J6" t="s">
         <v>122</v>
@@ -1013,13 +1013,16 @@
         <v>33</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="N6">
         <v>0</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="P6">
+        <v>6062.01</v>
       </c>
       <c r="Q6" t="s">
         <v>123</v>
@@ -1039,16 +1042,16 @@
         <v>79</v>
       </c>
       <c r="E7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H7">
-        <v>1086</v>
+        <v>2412</v>
       </c>
       <c r="I7">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="J7" t="s">
         <v>122</v>
@@ -1057,16 +1060,16 @@
         <v>33</v>
       </c>
       <c r="M7">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="N7">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O7">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="P7">
-        <v>74421.91</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="s">
         <v>123</v>
@@ -1086,16 +1089,16 @@
         <v>80</v>
       </c>
       <c r="E8" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F8" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="H8">
-        <v>2412</v>
+        <v>603</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8" t="s">
         <v>122</v>
@@ -1107,13 +1110,13 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>2401.47</v>
       </c>
       <c r="Q8" t="s">
         <v>123</v>
@@ -1133,16 +1136,16 @@
         <v>81</v>
       </c>
       <c r="E9" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F9" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H9">
-        <v>1244</v>
+        <v>1695</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J9" t="s">
         <v>122</v>
@@ -1154,10 +1157,13 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P9">
+        <v>40313.01</v>
       </c>
       <c r="Q9" t="s">
         <v>123</v>
@@ -1177,16 +1183,16 @@
         <v>82</v>
       </c>
       <c r="E10" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F10" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="H10">
-        <v>1477</v>
+        <v>1749</v>
       </c>
       <c r="I10">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J10" t="s">
         <v>122</v>
@@ -1195,16 +1201,16 @@
         <v>33</v>
       </c>
       <c r="M10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10">
-        <v>15250.32</v>
+        <v>9144.809999999999</v>
       </c>
       <c r="Q10" t="s">
         <v>123</v>
@@ -1227,13 +1233,13 @@
         <v>104</v>
       </c>
       <c r="F11" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="H11">
-        <v>3491</v>
+        <v>1086</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="J11" t="s">
         <v>122</v>
@@ -1242,13 +1248,16 @@
         <v>33</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="P11">
+        <v>74421.91</v>
       </c>
       <c r="Q11" t="s">
         <v>123</v>
@@ -1268,16 +1277,16 @@
         <v>84</v>
       </c>
       <c r="E12" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F12" t="s">
         <v>113</v>
       </c>
       <c r="H12">
-        <v>1174</v>
+        <v>1327</v>
       </c>
       <c r="I12">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="J12" t="s">
         <v>122</v>
@@ -1286,16 +1295,16 @@
         <v>33</v>
       </c>
       <c r="M12">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="N12">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="O12">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="P12">
-        <v>74740.39999999999</v>
+        <v>87327.06</v>
       </c>
       <c r="Q12" t="s">
         <v>123</v>
@@ -1315,16 +1324,16 @@
         <v>85</v>
       </c>
       <c r="E13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F13" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="H13">
-        <v>2412</v>
+        <v>1477</v>
       </c>
       <c r="I13">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J13" t="s">
         <v>122</v>
@@ -1336,13 +1345,13 @@
         <v>2</v>
       </c>
       <c r="N13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P13">
-        <v>13743.63</v>
+        <v>15250.32</v>
       </c>
       <c r="Q13" t="s">
         <v>123</v>
@@ -1362,16 +1371,16 @@
         <v>86</v>
       </c>
       <c r="E14" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F14" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="H14">
-        <v>1206</v>
+        <v>965</v>
       </c>
       <c r="I14">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="J14" t="s">
         <v>122</v>
@@ -1380,16 +1389,16 @@
         <v>33</v>
       </c>
       <c r="M14">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="N14">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="O14">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="P14">
-        <v>64858.18</v>
+        <v>2333.97</v>
       </c>
       <c r="Q14" t="s">
         <v>123</v>
@@ -1412,13 +1421,13 @@
         <v>105</v>
       </c>
       <c r="F15" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H15">
-        <v>1930</v>
+        <v>3491</v>
       </c>
       <c r="I15">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J15" t="s">
         <v>122</v>
@@ -1430,13 +1439,10 @@
         <v>0</v>
       </c>
       <c r="N15">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O15">
-        <v>1</v>
-      </c>
-      <c r="P15">
-        <v>12931.87</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="s">
         <v>123</v>
@@ -1456,16 +1462,16 @@
         <v>88</v>
       </c>
       <c r="E16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F16" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H16">
-        <v>1206</v>
+        <v>1568</v>
       </c>
       <c r="I16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J16" t="s">
         <v>122</v>
@@ -1474,16 +1480,16 @@
         <v>33</v>
       </c>
       <c r="M16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N16">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P16">
-        <v>5253.47</v>
+        <v>9786.09</v>
       </c>
       <c r="Q16" t="s">
         <v>123</v>
@@ -1506,13 +1512,13 @@
         <v>104</v>
       </c>
       <c r="F17" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H17">
-        <v>790</v>
+        <v>3015</v>
       </c>
       <c r="I17">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="J17" t="s">
         <v>122</v>
@@ -1521,16 +1527,13 @@
         <v>33</v>
       </c>
       <c r="M17">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="N17">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="O17">
-        <v>8</v>
-      </c>
-      <c r="P17">
-        <v>112587.51</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="s">
         <v>123</v>
@@ -1550,16 +1553,16 @@
         <v>90</v>
       </c>
       <c r="E18" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F18" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H18">
-        <v>1327</v>
+        <v>1930</v>
       </c>
       <c r="I18">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="J18" t="s">
         <v>122</v>
@@ -1568,16 +1571,16 @@
         <v>33</v>
       </c>
       <c r="M18">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="N18">
         <v>2</v>
       </c>
       <c r="O18">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="P18">
-        <v>82612.59</v>
+        <v>9925.940000000001</v>
       </c>
       <c r="Q18" t="s">
         <v>123</v>
@@ -1597,16 +1600,16 @@
         <v>91</v>
       </c>
       <c r="E19" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F19" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="H19">
-        <v>603</v>
+        <v>1688</v>
       </c>
       <c r="I19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J19" t="s">
         <v>122</v>
@@ -1618,13 +1621,10 @@
         <v>0</v>
       </c>
       <c r="N19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O19">
         <v>0</v>
-      </c>
-      <c r="P19">
-        <v>2401.47</v>
       </c>
       <c r="Q19" t="s">
         <v>123</v>
@@ -1647,13 +1647,13 @@
         <v>105</v>
       </c>
       <c r="F20" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H20">
-        <v>1689</v>
+        <v>848</v>
       </c>
       <c r="I20">
-        <v>4</v>
+        <v>111</v>
       </c>
       <c r="J20" t="s">
         <v>122</v>
@@ -1662,16 +1662,16 @@
         <v>33</v>
       </c>
       <c r="M20">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="O20">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P20">
-        <v>8082.68</v>
+        <v>145654.35</v>
       </c>
       <c r="Q20" t="s">
         <v>123</v>
@@ -1697,7 +1697,7 @@
         <v>118</v>
       </c>
       <c r="H21">
-        <v>1930</v>
+        <v>2412</v>
       </c>
       <c r="I21">
         <v>4</v>
@@ -1709,16 +1709,16 @@
         <v>33</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P21">
-        <v>9925.940000000001</v>
+        <v>13743.63</v>
       </c>
       <c r="Q21" t="s">
         <v>123</v>
@@ -1741,13 +1741,13 @@
         <v>105</v>
       </c>
       <c r="F22" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="H22">
-        <v>1749</v>
+        <v>1244</v>
       </c>
       <c r="I22">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J22" t="s">
         <v>122</v>
@@ -1759,13 +1759,10 @@
         <v>0</v>
       </c>
       <c r="N22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O22">
         <v>0</v>
-      </c>
-      <c r="P22">
-        <v>9144.809999999999</v>
       </c>
       <c r="Q22" t="s">
         <v>123</v>
@@ -1788,13 +1785,13 @@
         <v>103</v>
       </c>
       <c r="F23" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="H23">
-        <v>1108</v>
+        <v>1174</v>
       </c>
       <c r="I23">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="J23" t="s">
         <v>122</v>
@@ -1803,16 +1800,16 @@
         <v>33</v>
       </c>
       <c r="M23">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P23">
-        <v>62167.94</v>
+        <v>74740.39999999999</v>
       </c>
       <c r="Q23" t="s">
         <v>123</v>
@@ -1832,16 +1829,16 @@
         <v>96</v>
       </c>
       <c r="E24" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F24" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="H24">
-        <v>1568</v>
+        <v>1206</v>
       </c>
       <c r="I24">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="J24" t="s">
         <v>122</v>
@@ -1850,16 +1847,16 @@
         <v>33</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N24">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="P24">
-        <v>9786.09</v>
+        <v>61760.14</v>
       </c>
       <c r="Q24" t="s">
         <v>123</v>
@@ -1879,16 +1876,16 @@
         <v>97</v>
       </c>
       <c r="E25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F25" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="H25">
-        <v>1695</v>
+        <v>1930</v>
       </c>
       <c r="I25">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="J25" t="s">
         <v>122</v>
@@ -1900,13 +1897,13 @@
         <v>0</v>
       </c>
       <c r="N25">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O25">
         <v>1</v>
       </c>
       <c r="P25">
-        <v>44556.49</v>
+        <v>12931.87</v>
       </c>
       <c r="Q25" t="s">
         <v>123</v>
@@ -1926,13 +1923,13 @@
         <v>98</v>
       </c>
       <c r="E26" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F26" t="s">
         <v>120</v>
       </c>
       <c r="H26">
-        <v>3015</v>
+        <v>845</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -1944,12 +1941,15 @@
         <v>33</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N26">
         <v>0</v>
       </c>
       <c r="O26">
+        <v>2</v>
+      </c>
+      <c r="P26">
         <v>0</v>
       </c>
       <c r="Q26" t="s">
@@ -1973,13 +1973,13 @@
         <v>105</v>
       </c>
       <c r="F27" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H27">
-        <v>4423</v>
+        <v>927</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J27" t="s">
         <v>122</v>
@@ -1991,13 +1991,13 @@
         <v>0</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O27">
         <v>1</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>28085.93</v>
       </c>
       <c r="Q27" t="s">
         <v>123</v>
@@ -2017,16 +2017,16 @@
         <v>100</v>
       </c>
       <c r="E28" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F28" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="H28">
-        <v>927</v>
+        <v>790</v>
       </c>
       <c r="I28">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="J28" t="s">
         <v>122</v>
@@ -2035,16 +2035,16 @@
         <v>33</v>
       </c>
       <c r="M28">
+        <v>30</v>
+      </c>
+      <c r="N28">
+        <v>29</v>
+      </c>
+      <c r="O28">
         <v>8</v>
       </c>
-      <c r="N28">
-        <v>9</v>
-      </c>
-      <c r="O28">
-        <v>1</v>
-      </c>
       <c r="P28">
-        <v>26469.52</v>
+        <v>77357.00999999999</v>
       </c>
       <c r="Q28" t="s">
         <v>123</v>
@@ -2064,13 +2064,13 @@
         <v>101</v>
       </c>
       <c r="E29" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F29" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="H29">
-        <v>845</v>
+        <v>4423</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -2082,13 +2082,13 @@
         <v>33</v>
       </c>
       <c r="M29">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N29">
         <v>0</v>
       </c>
       <c r="O29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P29">
         <v>0</v>
